--- a/z_Java_Developer_Interview_Topics.xlsx
+++ b/z_Java_Developer_Interview_Topics.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Swayam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VIT Pune '27\CS Fundamentals\Apti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57491E20-6FD8-427E-B32C-26361E152DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A89731C5-3768-4C81-A928-E6274974A069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Mine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="79">
   <si>
     <t>Category</t>
   </si>
@@ -248,6 +249,15 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>Code</t>
   </si>
 </sst>
 </file>
@@ -271,12 +281,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -306,10 +328,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1172,4 +1206,583 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2F266F-7ADC-49A6-95D0-CE353160313E}">
+  <dimension ref="A1:F66"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/z_Java_Developer_Interview_Topics.xlsx
+++ b/z_Java_Developer_Interview_Topics.xlsx
@@ -328,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -340,9 +340,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1325,7 +1322,7 @@
       <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>73</v>
       </c>
     </row>
